--- a/projects/LTC7890_Buck/LTC7890_BOM.xlsx
+++ b/projects/LTC7890_Buck/LTC7890_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LTC7890_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC1EFA2D-106E-4BDF-BCA9-EF07F0B0975B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9255A2C-860C-4759-B1C6-64A57499660A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="125">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -122,12 +122,6 @@
     <t>Heat Sink</t>
   </si>
   <si>
-    <t>https://www.digikey.ca/en/products/detail/adafruit-industries-llc/1468/7241459</t>
-  </si>
-  <si>
-    <t>Heat Sink Tape</t>
-  </si>
-  <si>
     <t>RT0603FRE073K3L</t>
   </si>
   <si>
@@ -311,9 +305,6 @@
     <t>https://www.lcsc.com/product-detail/C95177.html</t>
   </si>
   <si>
-    <t>*8 out of 100</t>
-  </si>
-  <si>
     <t>*3 out of 50</t>
   </si>
   <si>
@@ -329,12 +320,6 @@
     <t>https://www.mouser.ca/ProductDetail/Same-Sky/SLW-1478144-5A-S-D</t>
   </si>
   <si>
-    <t>RC0603FR-0747RL</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C114623.html</t>
-  </si>
-  <si>
     <t>RT0603FRE07220KL</t>
   </si>
   <si>
@@ -365,9 +350,6 @@
     <t>https://www.lcsc.com/product-detail/C3885982.html</t>
   </si>
   <si>
-    <t>*12 out of 50</t>
-  </si>
-  <si>
     <t>https://www.lcsc.com/product-detail/C389010.html</t>
   </si>
   <si>
@@ -405,6 +387,30 @@
   </si>
   <si>
     <t>https://www.lcsc.com/product-detail/C472802.html</t>
+  </si>
+  <si>
+    <t>*4 out of 100</t>
+  </si>
+  <si>
+    <t>RC0603FR-071RL</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C112305.html</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/MG-Chemicals/8329TCS-6ML</t>
+  </si>
+  <si>
+    <t>8329TCS-6ML</t>
+  </si>
+  <si>
+    <t>RC0603FR-07100RL</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C105588.html</t>
+  </si>
+  <si>
+    <t>*18 out of 50</t>
   </si>
 </sst>
 </file>
@@ -778,7 +784,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E459BF-586A-4F4B-931A-B6F36BAD946F}">
-  <dimension ref="A1:U55"/>
+  <dimension ref="A1:U56"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
@@ -797,10 +803,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -815,7 +821,7 @@
         <v/>
       </c>
       <c r="R2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="U2">
         <v>1.37</v>
@@ -823,7 +829,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -836,7 +842,7 @@
         <v>12.82</v>
       </c>
       <c r="F3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
@@ -850,10 +856,10 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -866,7 +872,7 @@
         <v>7.68</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -892,26 +898,26 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B7" t="s">
         <v>14</v>
       </c>
       <c r="C7">
-        <v>0.24</v>
+        <v>0.36</v>
       </c>
       <c r="D7" s="1">
         <v>0.33</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
-        <v>0.10850400000000002</v>
+        <v>0.16275600000000001</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="Q7" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
@@ -925,10 +931,10 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -941,7 +947,7 @@
         <v>4.6399999999999997</v>
       </c>
       <c r="F9" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
@@ -962,12 +968,12 @@
         <v>0.93160000000000009</v>
       </c>
       <c r="F10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E11" s="1" t="str">
         <f>IF(COUNT(C11:D11)=2,D11*C11*IF(ISNUMBER(SEARCH("lcsc", F11)), U$2, 1),"")</f>
@@ -976,7 +982,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -989,12 +995,12 @@
         <v>25.24</v>
       </c>
       <c r="F12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
@@ -1011,14 +1017,14 @@
         <v>0.32</v>
       </c>
       <c r="E14" s="1">
-        <f t="shared" ref="E14:E44" si="2">IF(COUNT(C14:D14)=2,D14*C14*IF(ISNUMBER(SEARCH("lcsc", F14)), U$2, 1),"")</f>
+        <f t="shared" ref="E14:E33" si="2">IF(COUNT(C14:D14)=2,D14*C14*IF(ISNUMBER(SEARCH("lcsc", F14)), U$2, 1),"")</f>
         <v>2.6304000000000001E-2</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="Q14" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
@@ -1036,18 +1042,18 @@
         <v>6.9870000000000015E-2</v>
       </c>
       <c r="F15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="Q15" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C16">
         <v>0.04</v>
@@ -1060,10 +1066,10 @@
         <v>2.8496000000000004E-2</v>
       </c>
       <c r="F16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q16" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
@@ -1077,7 +1083,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -1093,7 +1099,7 @@
         <v>8.1926000000000005</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
@@ -1107,10 +1113,10 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B20" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C20">
         <v>0.4</v>
@@ -1123,10 +1129,10 @@
         <v>0.73980000000000012</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
@@ -1147,12 +1153,12 @@
         <v>17.1524</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B22" t="s">
         <v>16</v>
@@ -1168,19 +1174,19 @@
         <v>1.7262000000000003E-2</v>
       </c>
       <c r="F22" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q22" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B23" t="str">
-        <f>TEXT("47", "#")</f>
-        <v>47</v>
+        <f>TEXT("100", "#")</f>
+        <v>100</v>
       </c>
       <c r="C23">
         <v>0.02</v>
@@ -1193,10 +1199,10 @@
         <v>3.8360000000000009E-3</v>
       </c>
       <c r="F23" t="s">
-        <v>98</v>
+        <v>123</v>
       </c>
       <c r="Q23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
@@ -1210,7 +1216,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1223,25 +1229,25 @@
         <v>2.76</v>
       </c>
       <c r="F25" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>121</v>
       </c>
       <c r="C26">
-        <v>0.01</v>
+        <v>1E-3</v>
       </c>
       <c r="D26" s="1">
-        <v>6.94</v>
+        <v>41.36</v>
       </c>
       <c r="E26" s="1">
         <f t="shared" si="2"/>
-        <v>6.9400000000000003E-2</v>
+        <v>4.1360000000000001E-2</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>120</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
@@ -1255,10 +1261,10 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="B28" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="C28">
         <v>0.02</v>
@@ -1271,18 +1277,18 @@
         <v>1.3974000000000002E-2</v>
       </c>
       <c r="F28" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="Q28" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B29" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="C29">
         <v>0.02</v>
@@ -1295,18 +1301,18 @@
         <v>2.2467999999999998E-2</v>
       </c>
       <c r="F29" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="Q29" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="C30">
         <v>0.02</v>
@@ -1319,10 +1325,10 @@
         <v>1.6988E-2</v>
       </c>
       <c r="F30" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="Q30" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
@@ -1336,7 +1342,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="B32" t="s">
         <v>11</v>
@@ -1352,414 +1358,439 @@
         <v>9.7269999999999995E-2</v>
       </c>
       <c r="F32" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="Q32" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>88</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>89</v>
+        <v>118</v>
+      </c>
+      <c r="B33" t="str">
+        <f>TEXT("1", "#")</f>
+        <v>1</v>
       </c>
       <c r="C33">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="D33" s="1">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="E33" s="1">
         <f t="shared" si="2"/>
-        <v>1.3152E-2</v>
+        <v>1.8632000000000003E-2</v>
       </c>
       <c r="F33" t="s">
-        <v>90</v>
+        <v>119</v>
       </c>
       <c r="Q33" t="s">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>69</v>
-      </c>
-      <c r="B34" t="s">
-        <v>14</v>
-      </c>
-      <c r="C34" t="s">
-        <v>54</v>
-      </c>
-      <c r="E34" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>86</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C34">
+        <v>0.04</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="E34" s="1">
+        <f t="shared" ref="E34:E45" si="3">IF(COUNT(C34:D34)=2,D34*C34*IF(ISNUMBER(SEARCH("lcsc", F34)), U$2, 1),"")</f>
+        <v>6.5760000000000002E-3</v>
+      </c>
+      <c r="F34" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C35">
-        <v>0.04</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E35" s="1">
-        <f t="shared" si="2"/>
-        <v>1.6440000000000003E-2</v>
-      </c>
-      <c r="F35" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>75</v>
+        <v>14</v>
+      </c>
+      <c r="C35" t="s">
+        <v>52</v>
+      </c>
+      <c r="E35" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>48</v>
-      </c>
-      <c r="C36" t="s">
-        <v>32</v>
-      </c>
-      <c r="E36" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>95</v>
+      </c>
+      <c r="C36">
+        <v>0.04</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="3"/>
+        <v>1.6440000000000003E-2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C37">
-        <v>0.02</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E37" s="1">
-        <f t="shared" si="2"/>
-        <v>1.5070000000000004E-2</v>
-      </c>
-      <c r="F37" t="s">
         <v>46</v>
       </c>
-      <c r="Q37" t="s">
-        <v>39</v>
+      <c r="C37" t="s">
+        <v>30</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>102</v>
+        <v>48</v>
       </c>
       <c r="B38" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="C38">
         <v>0.02</v>
       </c>
       <c r="D38" s="1">
-        <v>0.52</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E38" s="1">
-        <f t="shared" si="2"/>
-        <v>1.4248000000000002E-2</v>
+        <f t="shared" si="3"/>
+        <v>1.5070000000000004E-2</v>
       </c>
       <c r="F38" t="s">
-        <v>104</v>
+        <v>44</v>
       </c>
       <c r="Q38" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="B39" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="C39">
         <v>0.02</v>
       </c>
       <c r="D39" s="1">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="E39" s="1">
-        <f t="shared" si="2"/>
-        <v>1.3974000000000002E-2</v>
+        <f t="shared" si="3"/>
+        <v>1.4248000000000002E-2</v>
       </c>
       <c r="F39" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="Q39" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>52</v>
+        <v>100</v>
+      </c>
+      <c r="B40" t="s">
+        <v>101</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="D40" s="1">
-        <v>0.23</v>
+        <v>0.51</v>
       </c>
       <c r="E40" s="1">
-        <f t="shared" si="2"/>
-        <v>0.23</v>
+        <f t="shared" si="3"/>
+        <v>1.3974000000000002E-2</v>
       </c>
       <c r="F40" t="s">
-        <v>53</v>
+        <v>102</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B41" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C41">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="D41" s="1">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="E41" s="1">
-        <f t="shared" si="2"/>
-        <v>4.2744000000000004E-2</v>
+        <f t="shared" si="3"/>
+        <v>0.23</v>
       </c>
       <c r="F41" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>92</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>28</v>
+      </c>
+      <c r="B42" t="s">
+        <v>29</v>
       </c>
       <c r="C42">
-        <v>0.8</v>
+        <v>0.06</v>
       </c>
       <c r="D42" s="1">
-        <v>0.39</v>
+        <v>0.52</v>
       </c>
       <c r="E42" s="1">
-        <f t="shared" si="2"/>
-        <v>0.4274400000000001</v>
+        <f t="shared" si="3"/>
+        <v>4.2744000000000004E-2</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="Q42" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>76</v>
-      </c>
-      <c r="E43" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>54</v>
+      </c>
+      <c r="C43">
+        <v>0.8</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="E43" s="1">
+        <f t="shared" si="3"/>
+        <v>0.4274400000000001</v>
+      </c>
+      <c r="F43" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>22</v>
-      </c>
-      <c r="C44">
-        <v>1</v>
-      </c>
-      <c r="D44" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="E44" s="1">
-        <f t="shared" si="2"/>
-        <v>0.91790000000000016</v>
-      </c>
-      <c r="F44" t="s">
-        <v>38</v>
+        <v>74</v>
+      </c>
+      <c r="E44" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>24</v>
-      </c>
-      <c r="B45" t="s">
-        <v>25</v>
-      </c>
-      <c r="C45" t="s">
-        <v>32</v>
+        <v>22</v>
+      </c>
+      <c r="C45">
+        <v>1</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E45" s="1">
+        <f t="shared" si="3"/>
+        <v>0.91790000000000016</v>
+      </c>
+      <c r="F45" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46" t="s">
+        <v>25</v>
+      </c>
+      <c r="C46" t="s">
         <v>30</v>
-      </c>
-      <c r="B46" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" t="s">
-        <v>54</v>
-      </c>
-      <c r="E46" s="1" t="str">
-        <f>IF(COUNT(C46:D46)=2,D46*C46*IF(ISNUMBER(SEARCH("lcsc", F46)), U$2, 1),"")</f>
-        <v/>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>87</v>
-      </c>
-      <c r="B47" t="str">
+        <v>28</v>
+      </c>
+      <c r="B47" t="s">
+        <v>29</v>
+      </c>
+      <c r="C47" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="1" t="str">
+        <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" t="str">
         <f>TEXT("10", "#")</f>
         <v>10</v>
       </c>
-      <c r="C47">
+      <c r="C48">
         <v>0.4</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D48" s="1">
         <v>0.94</v>
       </c>
-      <c r="E47" s="1">
-        <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
+      <c r="E48" s="1">
+        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
         <v>0.51512000000000002</v>
       </c>
-      <c r="F47" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>69</v>
-      </c>
-      <c r="B48" t="s">
-        <v>14</v>
-      </c>
-      <c r="C48" t="s">
-        <v>32</v>
-      </c>
-      <c r="E48" s="1" t="str">
-        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
-        <v/>
+      <c r="F48" t="s">
+        <v>80</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>77</v>
+        <v>67</v>
+      </c>
+      <c r="B49" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" t="s">
+        <v>30</v>
+      </c>
+      <c r="E49" s="1" t="str">
+        <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>51</v>
-      </c>
-      <c r="C50">
-        <v>2</v>
-      </c>
-      <c r="D50" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="E50" s="1">
-        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F50" t="s">
-        <v>96</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>33</v>
-      </c>
-      <c r="E51" s="1" t="str">
+        <v>49</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E51" s="1">
         <f>IF(COUNT(C51:D51)=2,D51*C51*IF(ISNUMBER(SEARCH("lcsc", F51)), U$2, 1),"")</f>
-        <v/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F51" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>78</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="E52" s="1">
+        <v>31</v>
+      </c>
+      <c r="E52" s="1" t="str">
         <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
-        <v>0.64390000000000003</v>
-      </c>
-      <c r="F52" t="s">
-        <v>79</v>
+        <v/>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>35</v>
+        <v>76</v>
       </c>
       <c r="C53">
         <v>1</v>
       </c>
       <c r="D53" s="1">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="E53" s="1">
         <f>IF(COUNT(C53:D53)=2,D53*C53*IF(ISNUMBER(SEARCH("lcsc", F53)), U$2, 1),"")</f>
-        <v>0.68500000000000005</v>
+        <v>0.64390000000000003</v>
       </c>
       <c r="F53" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C54">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D54" s="1">
-        <v>1.27</v>
+        <v>0.5</v>
       </c>
       <c r="E54" s="1">
         <f>IF(COUNT(C54:D54)=2,D54*C54*IF(ISNUMBER(SEARCH("lcsc", F54)), U$2, 1),"")</f>
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="F54" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55">
+        <v>0.4</v>
+      </c>
+      <c r="D55" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="E55" s="1">
+        <f>IF(COUNT(C55:D55)=2,D55*C55*IF(ISNUMBER(SEARCH("lcsc", F55)), U$2, 1),"")</f>
         <v>0.69596000000000002</v>
       </c>
-      <c r="F54" t="s">
-        <v>80</v>
-      </c>
-      <c r="Q54" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="D55" s="1" t="s">
+      <c r="F55" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D56" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E55" s="1">
-        <f>SUM(E2:E54)</f>
-        <v>91.541720000000026</v>
+      <c r="E56" s="1">
+        <f>SUM(E2:E55)</f>
+        <v>91.579988000000014</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LTC7890_Buck/LTC7890_BOM.xlsx
+++ b/projects/LTC7890_Buck/LTC7890_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LTC7890_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9255A2C-860C-4759-B1C6-64A57499660A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905A86F6-F0B7-4DC8-AD46-A896F5A138AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -53,9 +53,6 @@
     <t>CL32B475KCJZ4NE</t>
   </si>
   <si>
-    <t>https://www.digikey.ca/en/products/detail/samsung-electro-mechanics/CL32B475KCJZ4NE/27519552</t>
-  </si>
-  <si>
     <t>Capacitor Out</t>
   </si>
   <si>
@@ -411,6 +408,9 @@
   </si>
   <si>
     <t>*18 out of 50</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Samsung-Electro-Mechanics/CL32B475KCJZ4NE</t>
   </si>
 </sst>
 </file>
@@ -797,16 +797,16 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -814,14 +814,14 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="1" t="str">
         <f t="shared" ref="E2" si="0">IF(COUNT(C2:D2)=2,D2*C2,"")</f>
         <v/>
       </c>
       <c r="R2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="U2">
         <v>1.37</v>
@@ -829,7 +829,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -842,7 +842,7 @@
         <v>12.82</v>
       </c>
       <c r="F3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
@@ -856,10 +856,10 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B5" t="s">
         <v>55</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -872,7 +872,7 @@
         <v>7.68</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -880,7 +880,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6">
         <v>8</v>
@@ -893,15 +893,15 @@
         <v>5.52</v>
       </c>
       <c r="F6" t="s">
-        <v>5</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C7">
         <v>0.36</v>
@@ -914,15 +914,15 @@
         <v>0.16275600000000001</v>
       </c>
       <c r="F7" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q7" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8" s="1" t="str">
         <f>IF(COUNT(C8:D8)=2,D8*C8*IF(ISNUMBER(SEARCH("lcsc", F8)), U$2, 1),"")</f>
@@ -931,10 +931,10 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" t="s">
         <v>106</v>
-      </c>
-      <c r="B9" t="s">
-        <v>107</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -947,15 +947,15 @@
         <v>4.6399999999999997</v>
       </c>
       <c r="F9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10">
         <v>4</v>
@@ -968,12 +968,12 @@
         <v>0.93160000000000009</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E11" s="1" t="str">
         <f>IF(COUNT(C11:D11)=2,D11*C11*IF(ISNUMBER(SEARCH("lcsc", F11)), U$2, 1),"")</f>
@@ -982,7 +982,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -995,20 +995,20 @@
         <v>25.24</v>
       </c>
       <c r="F12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" t="s">
         <v>24</v>
-      </c>
-      <c r="B14" t="s">
-        <v>25</v>
       </c>
       <c r="C14">
         <v>0.06</v>
@@ -1021,15 +1021,15 @@
         <v>2.6304000000000001E-2</v>
       </c>
       <c r="F14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C15">
         <v>0.1</v>
@@ -1042,18 +1042,18 @@
         <v>6.9870000000000015E-2</v>
       </c>
       <c r="F15" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q15" t="s">
         <v>38</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
+        <v>44</v>
+      </c>
+      <c r="B16" t="s">
         <v>45</v>
-      </c>
-      <c r="B16" t="s">
-        <v>46</v>
       </c>
       <c r="C16">
         <v>0.04</v>
@@ -1066,15 +1066,15 @@
         <v>2.8496000000000004E-2</v>
       </c>
       <c r="F16" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="Q16" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E17" s="1" t="str">
         <f t="shared" si="2"/>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C18">
         <v>2</v>
@@ -1099,12 +1099,12 @@
         <v>8.1926000000000005</v>
       </c>
       <c r="F18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E19" s="1" t="str">
         <f t="shared" si="2"/>
@@ -1113,10 +1113,10 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" t="s">
         <v>58</v>
-      </c>
-      <c r="B20" t="s">
-        <v>59</v>
       </c>
       <c r="C20">
         <v>0.4</v>
@@ -1129,18 +1129,18 @@
         <v>0.73980000000000012</v>
       </c>
       <c r="F20" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q20" t="s">
         <v>60</v>
-      </c>
-      <c r="Q20" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
         <v>19</v>
-      </c>
-      <c r="B21" t="s">
-        <v>20</v>
       </c>
       <c r="C21">
         <v>4</v>
@@ -1153,15 +1153,15 @@
         <v>17.1524</v>
       </c>
       <c r="F21" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B22" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C22">
         <v>0.02</v>
@@ -1174,15 +1174,15 @@
         <v>1.7262000000000003E-2</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B23" t="str">
         <f>TEXT("100", "#")</f>
@@ -1199,15 +1199,15 @@
         <v>3.8360000000000009E-3</v>
       </c>
       <c r="F23" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="Q23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" s="1" t="str">
         <f t="shared" si="2"/>
@@ -1216,7 +1216,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1229,12 +1229,12 @@
         <v>2.76</v>
       </c>
       <c r="F25" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C26">
         <v>1E-3</v>
@@ -1247,12 +1247,12 @@
         <v>4.1360000000000001E-2</v>
       </c>
       <c r="F26" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E27" s="1" t="str">
         <f t="shared" si="2"/>
@@ -1261,10 +1261,10 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
+        <v>108</v>
+      </c>
+      <c r="B28" t="s">
         <v>109</v>
-      </c>
-      <c r="B28" t="s">
-        <v>110</v>
       </c>
       <c r="C28">
         <v>0.02</v>
@@ -1277,18 +1277,18 @@
         <v>1.3974000000000002E-2</v>
       </c>
       <c r="F28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="Q28" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
         <v>112</v>
-      </c>
-      <c r="B29" t="s">
-        <v>113</v>
       </c>
       <c r="C29">
         <v>0.02</v>
@@ -1301,18 +1301,18 @@
         <v>2.2467999999999998E-2</v>
       </c>
       <c r="F29" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="Q29" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" t="s">
         <v>114</v>
-      </c>
-      <c r="B30" t="s">
-        <v>115</v>
       </c>
       <c r="C30">
         <v>0.02</v>
@@ -1325,15 +1325,15 @@
         <v>1.6988E-2</v>
       </c>
       <c r="F30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q30" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E31" s="1" t="str">
         <f t="shared" si="2"/>
@@ -1342,10 +1342,10 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C32">
         <v>0.1</v>
@@ -1358,15 +1358,15 @@
         <v>9.7269999999999995E-2</v>
       </c>
       <c r="F32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B33" t="str">
         <f>TEXT("1", "#")</f>
@@ -1383,18 +1383,18 @@
         <v>1.8632000000000003E-2</v>
       </c>
       <c r="F33" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q33" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>85</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="C34">
         <v>0.04</v>
@@ -1407,21 +1407,21 @@
         <v>6.5760000000000002E-3</v>
       </c>
       <c r="F34" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="Q34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E35" s="1" t="str">
         <f t="shared" si="3"/>
@@ -1430,10 +1430,10 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>93</v>
+      </c>
+      <c r="B36" t="s">
         <v>94</v>
-      </c>
-      <c r="B36" t="s">
-        <v>95</v>
       </c>
       <c r="C36">
         <v>0.04</v>
@@ -1446,21 +1446,21 @@
         <v>1.6440000000000003E-2</v>
       </c>
       <c r="F36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="Q36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>44</v>
+      </c>
+      <c r="B37" t="s">
         <v>45</v>
       </c>
-      <c r="B37" t="s">
-        <v>46</v>
-      </c>
       <c r="C37" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E37" s="1" t="str">
         <f t="shared" si="3"/>
@@ -1469,10 +1469,10 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B38" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C38">
         <v>0.02</v>
@@ -1485,18 +1485,18 @@
         <v>1.5070000000000004E-2</v>
       </c>
       <c r="F38" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="Q38" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
+        <v>96</v>
+      </c>
+      <c r="B39" t="s">
         <v>97</v>
-      </c>
-      <c r="B39" t="s">
-        <v>98</v>
       </c>
       <c r="C39">
         <v>0.02</v>
@@ -1509,18 +1509,18 @@
         <v>1.4248000000000002E-2</v>
       </c>
       <c r="F39" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q39" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" t="s">
         <v>100</v>
-      </c>
-      <c r="B40" t="s">
-        <v>101</v>
       </c>
       <c r="C40">
         <v>0.02</v>
@@ -1533,15 +1533,15 @@
         <v>1.3974000000000002E-2</v>
       </c>
       <c r="F40" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q40" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C41">
         <v>1</v>
@@ -1554,15 +1554,15 @@
         <v>0.23</v>
       </c>
       <c r="F41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
+        <v>27</v>
+      </c>
+      <c r="B42" t="s">
         <v>28</v>
-      </c>
-      <c r="B42" t="s">
-        <v>29</v>
       </c>
       <c r="C42">
         <v>0.06</v>
@@ -1575,15 +1575,15 @@
         <v>4.2744000000000004E-2</v>
       </c>
       <c r="F42" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q42" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C43">
         <v>0.8</v>
@@ -1596,15 +1596,15 @@
         <v>0.4274400000000001</v>
       </c>
       <c r="F43" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="Q43" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E44" s="1" t="str">
         <f t="shared" si="3"/>
@@ -1613,7 +1613,7 @@
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C45">
         <v>1</v>
@@ -1626,29 +1626,29 @@
         <v>0.91790000000000016</v>
       </c>
       <c r="F45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
+        <v>23</v>
+      </c>
+      <c r="B46" t="s">
         <v>24</v>
       </c>
-      <c r="B46" t="s">
-        <v>25</v>
-      </c>
       <c r="C46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>27</v>
+      </c>
+      <c r="B47" t="s">
         <v>28</v>
       </c>
-      <c r="B47" t="s">
-        <v>29</v>
-      </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E47" s="1" t="str">
         <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B48" t="str">
         <f>TEXT("10", "#")</f>
@@ -1674,21 +1674,21 @@
         <v>0.51512000000000002</v>
       </c>
       <c r="F48" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q48" t="s">
         <v>80</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C49" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E49" s="1" t="str">
         <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
@@ -1697,12 +1697,12 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -1715,12 +1715,12 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="F51" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E52" s="1" t="str">
         <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
@@ -1729,7 +1729,7 @@
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>1</v>
@@ -1742,12 +1742,12 @@
         <v>0.64390000000000003</v>
       </c>
       <c r="F53" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1760,12 +1760,12 @@
         <v>0.68500000000000005</v>
       </c>
       <c r="F54" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C55">
         <v>0.4</v>
@@ -1778,15 +1778,15 @@
         <v>0.69596000000000002</v>
       </c>
       <c r="F55" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q55" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="D56" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E56" s="1">
         <f>SUM(E2:E55)</f>

--- a/projects/LTC7890_Buck/LTC7890_BOM.xlsx
+++ b/projects/LTC7890_Buck/LTC7890_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LTC7890_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{905A86F6-F0B7-4DC8-AD46-A896F5A138AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA24CE4-5C3D-4702-86D2-0BCC7416AB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="127">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -411,6 +411,12 @@
   </si>
   <si>
     <t>https://www.mouser.ca/ProductDetail/Samsung-Electro-Mechanics/CL32B475KCJZ4NE</t>
+  </si>
+  <si>
+    <t>V3PM10-M3/H</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Vishay-Semiconductors/V3PM10-M3-H</t>
   </si>
 </sst>
 </file>
@@ -784,7 +790,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E459BF-586A-4F4B-931A-B6F36BAD946F}">
-  <dimension ref="A1:U56"/>
+  <dimension ref="A1:U57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
@@ -1017,7 +1023,7 @@
         <v>0.32</v>
       </c>
       <c r="E14" s="1">
-        <f t="shared" ref="E14:E33" si="2">IF(COUNT(C14:D14)=2,D14*C14*IF(ISNUMBER(SEARCH("lcsc", F14)), U$2, 1),"")</f>
+        <f t="shared" ref="E14:E32" si="2">IF(COUNT(C14:D14)=2,D14*C14*IF(ISNUMBER(SEARCH("lcsc", F14)), U$2, 1),"")</f>
         <v>2.6304000000000001E-2</v>
       </c>
       <c r="F14" t="s">
@@ -1342,72 +1348,66 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>104</v>
-      </c>
-      <c r="B32" t="s">
-        <v>10</v>
+        <v>125</v>
       </c>
       <c r="C32">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="D32" s="1">
-        <v>0.71</v>
+        <v>0.53</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" si="2"/>
-        <v>9.7269999999999995E-2</v>
+        <v>1.06</v>
       </c>
       <c r="F32" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
+        <v>104</v>
+      </c>
+      <c r="B33" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33">
+        <v>0.1</v>
+      </c>
+      <c r="D33" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="E33" s="1">
+        <f>IF(COUNT(C33:D33)=2,D33*C33*IF(ISNUMBER(SEARCH("lcsc", F33)), U$2, 1),"")</f>
+        <v>9.7269999999999995E-2</v>
+      </c>
+      <c r="F33" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
         <v>117</v>
       </c>
-      <c r="B33" t="str">
+      <c r="B34" t="str">
         <f>TEXT("1", "#")</f>
         <v>1</v>
       </c>
-      <c r="C33">
-        <v>0.04</v>
-      </c>
-      <c r="D33" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="E33" s="1">
-        <f t="shared" si="2"/>
-        <v>1.8632000000000003E-2</v>
-      </c>
-      <c r="F33" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>85</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="C34">
         <v>0.04</v>
       </c>
       <c r="D34" s="1">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="E34" s="1">
-        <f t="shared" ref="E34:E45" si="3">IF(COUNT(C34:D34)=2,D34*C34*IF(ISNUMBER(SEARCH("lcsc", F34)), U$2, 1),"")</f>
-        <v>6.5760000000000002E-3</v>
+        <f>IF(COUNT(C34:D34)=2,D34*C34*IF(ISNUMBER(SEARCH("lcsc", F34)), U$2, 1),"")</f>
+        <v>1.8632000000000003E-2</v>
       </c>
       <c r="F34" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="Q34" t="s">
         <v>116</v>
@@ -1415,101 +1415,101 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>66</v>
-      </c>
-      <c r="B35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C35" t="s">
-        <v>51</v>
-      </c>
-      <c r="E35" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>85</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35">
+        <v>0.04</v>
+      </c>
+      <c r="D35" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="E35" s="1">
+        <f>IF(COUNT(C35:D35)=2,D35*C35*IF(ISNUMBER(SEARCH("lcsc", F35)), U$2, 1),"")</f>
+        <v>6.5760000000000002E-3</v>
+      </c>
+      <c r="F35" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B36" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36">
-        <v>0.04</v>
-      </c>
-      <c r="D36" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E36" s="1">
-        <f t="shared" si="3"/>
-        <v>1.6440000000000003E-2</v>
-      </c>
-      <c r="F36" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>72</v>
+        <v>13</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="E36" s="1" t="str">
+        <f>IF(COUNT(C36:D36)=2,D36*C36*IF(ISNUMBER(SEARCH("lcsc", F36)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="B37" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>94</v>
+      </c>
+      <c r="C37">
+        <v>0.04</v>
+      </c>
+      <c r="D37" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E37" s="1">
+        <f>IF(COUNT(C37:D37)=2,D37*C37*IF(ISNUMBER(SEARCH("lcsc", F37)), U$2, 1),"")</f>
+        <v>1.6440000000000003E-2</v>
+      </c>
+      <c r="F37" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
-      </c>
-      <c r="C38">
-        <v>0.02</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E38" s="1">
-        <f t="shared" si="3"/>
-        <v>1.5070000000000004E-2</v>
-      </c>
-      <c r="F38" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>36</v>
+        <v>45</v>
+      </c>
+      <c r="C38" t="s">
+        <v>29</v>
+      </c>
+      <c r="E38" s="1" t="str">
+        <f>IF(COUNT(C38:D38)=2,D38*C38*IF(ISNUMBER(SEARCH("lcsc", F38)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="B39" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="C39">
         <v>0.02</v>
       </c>
       <c r="D39" s="1">
-        <v>0.52</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E39" s="1">
-        <f t="shared" si="3"/>
-        <v>1.4248000000000002E-2</v>
+        <f>IF(COUNT(C39:D39)=2,D39*C39*IF(ISNUMBER(SEARCH("lcsc", F39)), U$2, 1),"")</f>
+        <v>1.5070000000000004E-2</v>
       </c>
       <c r="F39" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="Q39" t="s">
         <v>36</v>
@@ -1517,23 +1517,23 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B40" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C40">
         <v>0.02</v>
       </c>
       <c r="D40" s="1">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="E40" s="1">
-        <f t="shared" si="3"/>
-        <v>1.3974000000000002E-2</v>
+        <f>IF(COUNT(C40:D40)=2,D40*C40*IF(ISNUMBER(SEARCH("lcsc", F40)), U$2, 1),"")</f>
+        <v>1.4248000000000002E-2</v>
       </c>
       <c r="F40" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q40" t="s">
         <v>36</v>
@@ -1541,256 +1541,280 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>49</v>
+        <v>99</v>
+      </c>
+      <c r="B41" t="s">
+        <v>100</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="D41" s="1">
-        <v>0.23</v>
+        <v>0.51</v>
       </c>
       <c r="E41" s="1">
-        <f t="shared" si="3"/>
-        <v>0.23</v>
+        <f>IF(COUNT(C41:D41)=2,D41*C41*IF(ISNUMBER(SEARCH("lcsc", F41)), U$2, 1),"")</f>
+        <v>1.3974000000000002E-2</v>
       </c>
       <c r="F41" t="s">
-        <v>50</v>
+        <v>101</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>27</v>
-      </c>
-      <c r="B42" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C42">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="D42" s="1">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="E42" s="1">
-        <f t="shared" si="3"/>
-        <v>4.2744000000000004E-2</v>
+        <f>IF(COUNT(C42:D42)=2,D42*C42*IF(ISNUMBER(SEARCH("lcsc", F42)), U$2, 1),"")</f>
+        <v>0.23</v>
       </c>
       <c r="F42" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q42" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>53</v>
+        <v>27</v>
+      </c>
+      <c r="B43" t="s">
+        <v>28</v>
       </c>
       <c r="C43">
-        <v>0.8</v>
+        <v>0.06</v>
       </c>
       <c r="D43" s="1">
-        <v>0.39</v>
+        <v>0.52</v>
       </c>
       <c r="E43" s="1">
-        <f t="shared" si="3"/>
-        <v>0.4274400000000001</v>
+        <f>IF(COUNT(C43:D43)=2,D43*C43*IF(ISNUMBER(SEARCH("lcsc", F43)), U$2, 1),"")</f>
+        <v>4.2744000000000004E-2</v>
       </c>
       <c r="F43" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="Q43" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>73</v>
-      </c>
-      <c r="E44" s="1" t="str">
-        <f t="shared" si="3"/>
-        <v/>
+        <v>53</v>
+      </c>
+      <c r="C44">
+        <v>0.8</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="E44" s="1">
+        <f>IF(COUNT(C44:D44)=2,D44*C44*IF(ISNUMBER(SEARCH("lcsc", F44)), U$2, 1),"")</f>
+        <v>0.4274400000000001</v>
+      </c>
+      <c r="F44" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>21</v>
-      </c>
-      <c r="C45">
-        <v>1</v>
-      </c>
-      <c r="D45" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="E45" s="1">
-        <f t="shared" si="3"/>
-        <v>0.91790000000000016</v>
-      </c>
-      <c r="F45" t="s">
-        <v>35</v>
+        <v>73</v>
+      </c>
+      <c r="E45" s="1" t="str">
+        <f>IF(COUNT(C45:D45)=2,D45*C45*IF(ISNUMBER(SEARCH("lcsc", F45)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>23</v>
-      </c>
-      <c r="B46" t="s">
-        <v>24</v>
-      </c>
-      <c r="C46" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E46" s="1">
+        <f>IF(COUNT(C46:D46)=2,D46*C46*IF(ISNUMBER(SEARCH("lcsc", F46)), U$2, 1),"")</f>
+        <v>0.91790000000000016</v>
+      </c>
+      <c r="F46" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
-      </c>
-      <c r="E47" s="1" t="str">
-        <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>27</v>
+      </c>
+      <c r="B48" t="s">
+        <v>28</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+      <c r="E48" s="1" t="str">
+        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
         <v>84</v>
       </c>
-      <c r="B48" t="str">
+      <c r="B49" t="str">
         <f>TEXT("10", "#")</f>
         <v>10</v>
       </c>
-      <c r="C48">
+      <c r="C49">
         <v>0.4</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D49" s="1">
         <v>0.94</v>
       </c>
-      <c r="E48" s="1">
-        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
+      <c r="E49" s="1">
+        <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
         <v>0.51512000000000002</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F49" t="s">
         <v>79</v>
       </c>
-      <c r="Q48" t="s">
+      <c r="Q49" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" t="s">
-        <v>13</v>
-      </c>
-      <c r="C49" t="s">
-        <v>29</v>
-      </c>
-      <c r="E49" s="1" t="str">
-        <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
-        <v/>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>74</v>
+        <v>66</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
+        <v>29</v>
+      </c>
+      <c r="E50" s="1" t="str">
+        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>48</v>
-      </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="E51" s="1">
-        <f>IF(COUNT(C51:D51)=2,D51*C51*IF(ISNUMBER(SEARCH("lcsc", F51)), U$2, 1),"")</f>
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F51" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>30</v>
-      </c>
-      <c r="E52" s="1" t="str">
+        <v>48</v>
+      </c>
+      <c r="C52">
+        <v>2</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E52" s="1">
         <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
-        <v/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F52" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="E53" s="1">
+        <v>30</v>
+      </c>
+      <c r="E53" s="1" t="str">
         <f>IF(COUNT(C53:D53)=2,D53*C53*IF(ISNUMBER(SEARCH("lcsc", F53)), U$2, 1),"")</f>
-        <v>0.64390000000000003</v>
-      </c>
-      <c r="F53" t="s">
-        <v>76</v>
+        <v/>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" s="1">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="E54" s="1">
         <f>IF(COUNT(C54:D54)=2,D54*C54*IF(ISNUMBER(SEARCH("lcsc", F54)), U$2, 1),"")</f>
-        <v>0.68500000000000005</v>
+        <v>0.64390000000000003</v>
       </c>
       <c r="F54" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C55">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D55" s="1">
-        <v>1.27</v>
+        <v>0.5</v>
       </c>
       <c r="E55" s="1">
         <f>IF(COUNT(C55:D55)=2,D55*C55*IF(ISNUMBER(SEARCH("lcsc", F55)), U$2, 1),"")</f>
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="F55" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56">
+        <v>0.4</v>
+      </c>
+      <c r="D56" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="E56" s="1">
+        <f>IF(COUNT(C56:D56)=2,D56*C56*IF(ISNUMBER(SEARCH("lcsc", F56)), U$2, 1),"")</f>
         <v>0.69596000000000002</v>
       </c>
-      <c r="F55" t="s">
+      <c r="F56" t="s">
         <v>77</v>
       </c>
-      <c r="Q55" t="s">
+      <c r="Q56" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="D56" s="1" t="s">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D57" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E56" s="1">
-        <f>SUM(E2:E55)</f>
-        <v>91.579988000000014</v>
+      <c r="E57" s="1">
+        <f>SUM(E2:E56)</f>
+        <v>92.639988000000017</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LTC7890_Buck/LTC7890_BOM.xlsx
+++ b/projects/LTC7890_Buck/LTC7890_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LTC7890_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CA24CE4-5C3D-4702-86D2-0BCC7416AB73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D2BE63-F245-4FA3-9EAF-01858338222B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="129">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -417,6 +417,12 @@
   </si>
   <si>
     <t>https://www.mouser.ca/ProductDetail/Vishay-Semiconductors/V3PM10-M3-H</t>
+  </si>
+  <si>
+    <t>RC0603FR-072R2L</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C112307.html</t>
   </si>
 </sst>
 </file>
@@ -452,10 +458,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -790,7 +797,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E459BF-586A-4F4B-931A-B6F36BAD946F}">
-  <dimension ref="A1:U57"/>
+  <dimension ref="A1:U58"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
@@ -1378,7 +1385,7 @@
         <v>0.71</v>
       </c>
       <c r="E33" s="1">
-        <f>IF(COUNT(C33:D33)=2,D33*C33*IF(ISNUMBER(SEARCH("lcsc", F33)), U$2, 1),"")</f>
+        <f t="shared" ref="E33" si="3">IF(COUNT(C33:D33)=2,D33*C33*IF(ISNUMBER(SEARCH("lcsc", F33)), U$2, 1),"")</f>
         <v>9.7269999999999995E-2</v>
       </c>
       <c r="F33" t="s">
@@ -1390,150 +1397,151 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
+        <v>127</v>
+      </c>
+      <c r="B34" t="str">
+        <f>TEXT("2.2", "#.#")</f>
+        <v>2.2</v>
+      </c>
+      <c r="C34">
+        <v>0.04</v>
+      </c>
+      <c r="D34" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="E34" s="1">
+        <f>IF(COUNT(C34:D34)=2,D34*C34*IF(ISNUMBER(SEARCH("lcsc", F34)), U$2, 1),"")</f>
+        <v>2.4660000000000005E-2</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>117</v>
       </c>
-      <c r="B34" t="str">
+      <c r="B35" t="str">
         <f>TEXT("1", "#")</f>
         <v>1</v>
       </c>
-      <c r="C34">
-        <v>0.04</v>
-      </c>
-      <c r="D34" s="1">
-        <v>0.34</v>
-      </c>
-      <c r="E34" s="1">
-        <f>IF(COUNT(C34:D34)=2,D34*C34*IF(ISNUMBER(SEARCH("lcsc", F34)), U$2, 1),"")</f>
-        <v>1.8632000000000003E-2</v>
-      </c>
-      <c r="F34" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>85</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="C35">
         <v>0.04</v>
       </c>
       <c r="D35" s="1">
-        <v>0.12</v>
+        <v>0.34</v>
       </c>
       <c r="E35" s="1">
         <f>IF(COUNT(C35:D35)=2,D35*C35*IF(ISNUMBER(SEARCH("lcsc", F35)), U$2, 1),"")</f>
-        <v>6.5760000000000002E-3</v>
+        <v>1.8632000000000003E-2</v>
       </c>
       <c r="F35" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="Q35" t="s">
-        <v>116</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" t="s">
-        <v>51</v>
-      </c>
-      <c r="E36" s="1" t="str">
+        <v>85</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36">
+        <v>0.04</v>
+      </c>
+      <c r="D36" s="1">
+        <v>0.12</v>
+      </c>
+      <c r="E36" s="1">
         <f>IF(COUNT(C36:D36)=2,D36*C36*IF(ISNUMBER(SEARCH("lcsc", F36)), U$2, 1),"")</f>
-        <v/>
+        <v>6.5760000000000002E-3</v>
+      </c>
+      <c r="F36" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="B37" t="s">
-        <v>94</v>
-      </c>
-      <c r="C37">
-        <v>0.04</v>
-      </c>
-      <c r="D37" s="1">
-        <v>0.3</v>
-      </c>
-      <c r="E37" s="1">
+        <v>13</v>
+      </c>
+      <c r="C37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="1" t="str">
         <f>IF(COUNT(C37:D37)=2,D37*C37*IF(ISNUMBER(SEARCH("lcsc", F37)), U$2, 1),"")</f>
-        <v>1.6440000000000003E-2</v>
-      </c>
-      <c r="F37" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>72</v>
+        <v/>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>44</v>
+        <v>93</v>
       </c>
       <c r="B38" t="s">
-        <v>45</v>
-      </c>
-      <c r="C38" t="s">
-        <v>29</v>
-      </c>
-      <c r="E38" s="1" t="str">
+        <v>94</v>
+      </c>
+      <c r="C38">
+        <v>0.04</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="E38" s="1">
         <f>IF(COUNT(C38:D38)=2,D38*C38*IF(ISNUMBER(SEARCH("lcsc", F38)), U$2, 1),"")</f>
-        <v/>
+        <v>1.6440000000000003E-2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
-      </c>
-      <c r="C39">
-        <v>0.02</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E39" s="1">
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="E39" s="1" t="str">
         <f>IF(COUNT(C39:D39)=2,D39*C39*IF(ISNUMBER(SEARCH("lcsc", F39)), U$2, 1),"")</f>
-        <v>1.5070000000000004E-2</v>
-      </c>
-      <c r="F39" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>36</v>
+        <v/>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>96</v>
+        <v>47</v>
       </c>
       <c r="B40" t="s">
-        <v>97</v>
+        <v>20</v>
       </c>
       <c r="C40">
         <v>0.02</v>
       </c>
       <c r="D40" s="1">
-        <v>0.52</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E40" s="1">
         <f>IF(COUNT(C40:D40)=2,D40*C40*IF(ISNUMBER(SEARCH("lcsc", F40)), U$2, 1),"")</f>
-        <v>1.4248000000000002E-2</v>
+        <v>1.5070000000000004E-2</v>
       </c>
       <c r="F40" t="s">
-        <v>98</v>
+        <v>43</v>
       </c>
       <c r="Q40" t="s">
         <v>36</v>
@@ -1541,23 +1549,23 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B41" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C41">
         <v>0.02</v>
       </c>
       <c r="D41" s="1">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="E41" s="1">
         <f>IF(COUNT(C41:D41)=2,D41*C41*IF(ISNUMBER(SEARCH("lcsc", F41)), U$2, 1),"")</f>
-        <v>1.3974000000000002E-2</v>
+        <v>1.4248000000000002E-2</v>
       </c>
       <c r="F41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q41" t="s">
         <v>36</v>
@@ -1565,256 +1573,280 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>49</v>
+        <v>99</v>
+      </c>
+      <c r="B42" t="s">
+        <v>100</v>
       </c>
       <c r="C42">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="D42" s="1">
-        <v>0.23</v>
+        <v>0.51</v>
       </c>
       <c r="E42" s="1">
         <f>IF(COUNT(C42:D42)=2,D42*C42*IF(ISNUMBER(SEARCH("lcsc", F42)), U$2, 1),"")</f>
-        <v>0.23</v>
+        <v>1.3974000000000002E-2</v>
       </c>
       <c r="F42" t="s">
-        <v>50</v>
+        <v>101</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>27</v>
-      </c>
-      <c r="B43" t="s">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C43">
-        <v>0.06</v>
+        <v>1</v>
       </c>
       <c r="D43" s="1">
-        <v>0.52</v>
+        <v>0.23</v>
       </c>
       <c r="E43" s="1">
         <f>IF(COUNT(C43:D43)=2,D43*C43*IF(ISNUMBER(SEARCH("lcsc", F43)), U$2, 1),"")</f>
-        <v>4.2744000000000004E-2</v>
+        <v>0.23</v>
       </c>
       <c r="F43" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q43" t="s">
-        <v>88</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>27</v>
+      </c>
+      <c r="B44" t="s">
+        <v>28</v>
       </c>
       <c r="C44">
-        <v>0.8</v>
+        <v>0.06</v>
       </c>
       <c r="D44" s="1">
-        <v>0.39</v>
+        <v>0.52</v>
       </c>
       <c r="E44" s="1">
         <f>IF(COUNT(C44:D44)=2,D44*C44*IF(ISNUMBER(SEARCH("lcsc", F44)), U$2, 1),"")</f>
-        <v>0.4274400000000001</v>
+        <v>4.2744000000000004E-2</v>
       </c>
       <c r="F44" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="Q44" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>73</v>
-      </c>
-      <c r="E45" s="1" t="str">
+        <v>53</v>
+      </c>
+      <c r="C45">
+        <v>0.8</v>
+      </c>
+      <c r="D45" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="E45" s="1">
         <f>IF(COUNT(C45:D45)=2,D45*C45*IF(ISNUMBER(SEARCH("lcsc", F45)), U$2, 1),"")</f>
-        <v/>
+        <v>0.4274400000000001</v>
+      </c>
+      <c r="F45" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>21</v>
-      </c>
-      <c r="C46">
-        <v>1</v>
-      </c>
-      <c r="D46" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="E46" s="1">
+        <v>73</v>
+      </c>
+      <c r="E46" s="1" t="str">
         <f>IF(COUNT(C46:D46)=2,D46*C46*IF(ISNUMBER(SEARCH("lcsc", F46)), U$2, 1),"")</f>
-        <v>0.91790000000000016</v>
-      </c>
-      <c r="F46" t="s">
-        <v>35</v>
+        <v/>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>23</v>
-      </c>
-      <c r="B47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47" t="s">
-        <v>29</v>
+        <v>21</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E47" s="1">
+        <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
+        <v>0.91790000000000016</v>
+      </c>
+      <c r="F47" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B48" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
-      </c>
-      <c r="E48" s="1" t="str">
-        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
-        <v/>
+        <v>29</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
+        <v>27</v>
+      </c>
+      <c r="B49" t="s">
+        <v>28</v>
+      </c>
+      <c r="C49" t="s">
+        <v>51</v>
+      </c>
+      <c r="E49" s="1" t="str">
+        <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>84</v>
       </c>
-      <c r="B49" t="str">
+      <c r="B50" t="str">
         <f>TEXT("10", "#")</f>
         <v>10</v>
       </c>
-      <c r="C49">
+      <c r="C50">
         <v>0.4</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D50" s="1">
         <v>0.94</v>
       </c>
-      <c r="E49" s="1">
-        <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
+      <c r="E50" s="1">
+        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
         <v>0.51512000000000002</v>
       </c>
-      <c r="F49" t="s">
+      <c r="F50" t="s">
         <v>79</v>
       </c>
-      <c r="Q49" t="s">
+      <c r="Q50" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>66</v>
-      </c>
-      <c r="B50" t="s">
-        <v>13</v>
-      </c>
-      <c r="C50" t="s">
-        <v>29</v>
-      </c>
-      <c r="E50" s="1" t="str">
-        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
-        <v/>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>74</v>
+        <v>66</v>
+      </c>
+      <c r="B51" t="s">
+        <v>13</v>
+      </c>
+      <c r="C51" t="s">
+        <v>29</v>
+      </c>
+      <c r="E51" s="1" t="str">
+        <f>IF(COUNT(C51:D51)=2,D51*C51*IF(ISNUMBER(SEARCH("lcsc", F51)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>48</v>
-      </c>
-      <c r="C52">
-        <v>2</v>
-      </c>
-      <c r="D52" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="E52" s="1">
-        <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F52" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>30</v>
-      </c>
-      <c r="E53" s="1" t="str">
+        <v>48</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E53" s="1">
         <f>IF(COUNT(C53:D53)=2,D53*C53*IF(ISNUMBER(SEARCH("lcsc", F53)), U$2, 1),"")</f>
-        <v/>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F53" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>75</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="E54" s="1">
+        <v>30</v>
+      </c>
+      <c r="E54" s="1" t="str">
         <f>IF(COUNT(C54:D54)=2,D54*C54*IF(ISNUMBER(SEARCH("lcsc", F54)), U$2, 1),"")</f>
-        <v>0.64390000000000003</v>
-      </c>
-      <c r="F54" t="s">
-        <v>76</v>
+        <v/>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" s="1">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="E55" s="1">
         <f>IF(COUNT(C55:D55)=2,D55*C55*IF(ISNUMBER(SEARCH("lcsc", F55)), U$2, 1),"")</f>
-        <v>0.68500000000000005</v>
+        <v>0.64390000000000003</v>
       </c>
       <c r="F55" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C56">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D56" s="1">
-        <v>1.27</v>
+        <v>0.5</v>
       </c>
       <c r="E56" s="1">
         <f>IF(COUNT(C56:D56)=2,D56*C56*IF(ISNUMBER(SEARCH("lcsc", F56)), U$2, 1),"")</f>
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="F56" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57">
+        <v>0.4</v>
+      </c>
+      <c r="D57" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="E57" s="1">
+        <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
         <v>0.69596000000000002</v>
       </c>
-      <c r="F56" t="s">
+      <c r="F57" t="s">
         <v>77</v>
       </c>
-      <c r="Q56" t="s">
+      <c r="Q57" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="D57" s="1" t="s">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D58" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E57" s="1">
-        <f>SUM(E2:E56)</f>
-        <v>92.639988000000017</v>
+      <c r="E58" s="1">
+        <f>SUM(E2:E57)</f>
+        <v>92.664648000000014</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LTC7890_Buck/LTC7890_BOM.xlsx
+++ b/projects/LTC7890_Buck/LTC7890_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LTC7890_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50D2BE63-F245-4FA3-9EAF-01858338222B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243B72D3-0EB2-4F45-B68D-1E7300B3C5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="140">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -194,12 +194,6 @@
     <t>Tallied Above (3x)</t>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C5199801.html</t>
-  </si>
-  <si>
-    <t>RH-5001</t>
-  </si>
-  <si>
     <t>EKYC101ELL331MK25S</t>
   </si>
   <si>
@@ -272,9 +266,6 @@
     <t>https://www.lcsc.com/product-detail/C189895.html</t>
   </si>
   <si>
-    <t>*4 out of 5</t>
-  </si>
-  <si>
     <t>https://www.lcsc.com/product-detail/C861082.html</t>
   </si>
   <si>
@@ -423,6 +414,48 @@
   </si>
   <si>
     <t>https://www.lcsc.com/product-detail/C112307.html</t>
+  </si>
+  <si>
+    <t>RT0603FRD078K2L</t>
+  </si>
+  <si>
+    <t>8.2k</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C863965.html</t>
+  </si>
+  <si>
+    <t>Cooling</t>
+  </si>
+  <si>
+    <t>AUB0524VHD</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Delta-Electronics/AUB0524VHD</t>
+  </si>
+  <si>
+    <t>ADC101C021CIMM/NOPB</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Texas-Instruments/ADC101C021CIMM-NOPB</t>
+  </si>
+  <si>
+    <t>JSNB103F344FBEWH</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/kamaya-inc/JSNB103F344FBEWH/25863556</t>
+  </si>
+  <si>
+    <t>GSF3400</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/good-ark-semiconductor/GSF3400/18648343</t>
+  </si>
+  <si>
+    <t>CL-SB-13A-01T</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Nidec-Components/CL-SB-13A-01T</t>
   </si>
 </sst>
 </file>
@@ -458,11 +491,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -797,7 +829,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E459BF-586A-4F4B-931A-B6F36BAD946F}">
-  <dimension ref="A1:U58"/>
+  <dimension ref="A1:U64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
@@ -816,10 +848,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -834,7 +866,7 @@
         <v/>
       </c>
       <c r="R2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="U2">
         <v>1.37</v>
@@ -842,7 +874,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -855,7 +887,7 @@
         <v>12.82</v>
       </c>
       <c r="F3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
@@ -869,10 +901,10 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -885,7 +917,7 @@
         <v>7.68</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -906,12 +938,12 @@
         <v>5.52</v>
       </c>
       <c r="F6" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B7" t="s">
         <v>13</v>
@@ -927,10 +959,10 @@
         <v>0.16275600000000001</v>
       </c>
       <c r="F7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q7" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
@@ -944,10 +976,10 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -960,7 +992,7 @@
         <v>4.6399999999999997</v>
       </c>
       <c r="F9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
@@ -986,7 +1018,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="E11" s="1" t="str">
         <f>IF(COUNT(C11:D11)=2,D11*C11*IF(ISNUMBER(SEARCH("lcsc", F11)), U$2, 1),"")</f>
@@ -995,7 +1027,7 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C12">
         <v>4</v>
@@ -1008,12 +1040,12 @@
         <v>25.24</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
@@ -1037,7 +1069,7 @@
         <v>39</v>
       </c>
       <c r="Q14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
@@ -1082,7 +1114,7 @@
         <v>46</v>
       </c>
       <c r="Q16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
@@ -1096,7 +1128,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B18" t="s">
         <v>12</v>
@@ -1112,7 +1144,7 @@
         <v>8.1926000000000005</v>
       </c>
       <c r="F18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
@@ -1126,10 +1158,10 @@
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C20">
         <v>0.4</v>
@@ -1142,10 +1174,10 @@
         <v>0.73980000000000012</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="Q20" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
@@ -1171,7 +1203,7 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
@@ -1187,7 +1219,7 @@
         <v>1.7262000000000003E-2</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q22" t="s">
         <v>42</v>
@@ -1195,7 +1227,7 @@
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B23" t="str">
         <f>TEXT("100", "#")</f>
@@ -1212,7 +1244,7 @@
         <v>3.8360000000000009E-3</v>
       </c>
       <c r="F23" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="Q23" t="s">
         <v>42</v>
@@ -1229,7 +1261,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C25">
         <v>1</v>
@@ -1242,12 +1274,12 @@
         <v>2.76</v>
       </c>
       <c r="F25" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C26">
         <v>1E-3</v>
@@ -1260,7 +1292,7 @@
         <v>4.1360000000000001E-2</v>
       </c>
       <c r="F26" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
@@ -1274,10 +1306,10 @@
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="B28" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C28">
         <v>0.02</v>
@@ -1290,7 +1322,7 @@
         <v>1.3974000000000002E-2</v>
       </c>
       <c r="F28" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="Q28" t="s">
         <v>36</v>
@@ -1298,10 +1330,10 @@
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="B29" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C29">
         <v>0.02</v>
@@ -1314,7 +1346,7 @@
         <v>2.2467999999999998E-2</v>
       </c>
       <c r="F29" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="Q29" t="s">
         <v>36</v>
@@ -1322,10 +1354,10 @@
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="C30">
         <v>0.02</v>
@@ -1338,7 +1370,7 @@
         <v>1.6988E-2</v>
       </c>
       <c r="F30" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="Q30" t="s">
         <v>36</v>
@@ -1355,7 +1387,7 @@
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C32">
         <v>2</v>
@@ -1368,12 +1400,12 @@
         <v>1.06</v>
       </c>
       <c r="F32" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -1389,7 +1421,7 @@
         <v>9.7269999999999995E-2</v>
       </c>
       <c r="F33" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q33" t="s">
         <v>38</v>
@@ -1397,7 +1429,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="B34" t="str">
         <f>TEXT("2.2", "#.#")</f>
@@ -1410,11 +1442,11 @@
         <v>0.45</v>
       </c>
       <c r="E34" s="1">
-        <f>IF(COUNT(C34:D34)=2,D34*C34*IF(ISNUMBER(SEARCH("lcsc", F34)), U$2, 1),"")</f>
+        <f t="shared" ref="E34:E44" si="4">IF(COUNT(C34:D34)=2,D34*C34*IF(ISNUMBER(SEARCH("lcsc", F34)), U$2, 1),"")</f>
         <v>2.4660000000000005E-2</v>
       </c>
-      <c r="F34" s="3" t="s">
-        <v>128</v>
+      <c r="F34" t="s">
+        <v>125</v>
       </c>
       <c r="Q34" t="s">
         <v>42</v>
@@ -1422,7 +1454,7 @@
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B35" t="str">
         <f>TEXT("1", "#")</f>
@@ -1435,11 +1467,11 @@
         <v>0.34</v>
       </c>
       <c r="E35" s="1">
-        <f>IF(COUNT(C35:D35)=2,D35*C35*IF(ISNUMBER(SEARCH("lcsc", F35)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v>1.8632000000000003E-2</v>
       </c>
       <c r="F35" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="Q35" t="s">
         <v>42</v>
@@ -1447,10 +1479,10 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C36">
         <v>0.04</v>
@@ -1459,19 +1491,19 @@
         <v>0.12</v>
       </c>
       <c r="E36" s="1">
-        <f>IF(COUNT(C36:D36)=2,D36*C36*IF(ISNUMBER(SEARCH("lcsc", F36)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v>6.5760000000000002E-3</v>
       </c>
       <c r="F36" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="Q36" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -1480,16 +1512,16 @@
         <v>51</v>
       </c>
       <c r="E37" s="1" t="str">
-        <f>IF(COUNT(C37:D37)=2,D37*C37*IF(ISNUMBER(SEARCH("lcsc", F37)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B38" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C38">
         <v>0.04</v>
@@ -1498,14 +1530,14 @@
         <v>0.3</v>
       </c>
       <c r="E38" s="1">
-        <f>IF(COUNT(C38:D38)=2,D38*C38*IF(ISNUMBER(SEARCH("lcsc", F38)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v>1.6440000000000003E-2</v>
       </c>
       <c r="F38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="Q38" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
@@ -1519,7 +1551,7 @@
         <v>29</v>
       </c>
       <c r="E39" s="1" t="str">
-        <f>IF(COUNT(C39:D39)=2,D39*C39*IF(ISNUMBER(SEARCH("lcsc", F39)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
@@ -1537,7 +1569,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E40" s="1">
-        <f>IF(COUNT(C40:D40)=2,D40*C40*IF(ISNUMBER(SEARCH("lcsc", F40)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v>1.5070000000000004E-2</v>
       </c>
       <c r="F40" t="s">
@@ -1549,10 +1581,10 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C41">
         <v>0.02</v>
@@ -1561,11 +1593,11 @@
         <v>0.52</v>
       </c>
       <c r="E41" s="1">
-        <f>IF(COUNT(C41:D41)=2,D41*C41*IF(ISNUMBER(SEARCH("lcsc", F41)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v>1.4248000000000002E-2</v>
       </c>
       <c r="F41" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="Q41" t="s">
         <v>36</v>
@@ -1573,10 +1605,10 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C42">
         <v>0.02</v>
@@ -1585,11 +1617,11 @@
         <v>0.51</v>
       </c>
       <c r="E42" s="1">
-        <f>IF(COUNT(C42:D42)=2,D42*C42*IF(ISNUMBER(SEARCH("lcsc", F42)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v>1.3974000000000002E-2</v>
       </c>
       <c r="F42" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="Q42" t="s">
         <v>36</v>
@@ -1606,7 +1638,7 @@
         <v>0.23</v>
       </c>
       <c r="E43" s="1">
-        <f>IF(COUNT(C43:D43)=2,D43*C43*IF(ISNUMBER(SEARCH("lcsc", F43)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v>0.23</v>
       </c>
       <c r="F43" t="s">
@@ -1627,73 +1659,76 @@
         <v>0.52</v>
       </c>
       <c r="E44" s="1">
-        <f>IF(COUNT(C44:D44)=2,D44*C44*IF(ISNUMBER(SEARCH("lcsc", F44)), U$2, 1),"")</f>
+        <f t="shared" si="4"/>
         <v>4.2744000000000004E-2</v>
       </c>
       <c r="F44" t="s">
         <v>40</v>
       </c>
       <c r="Q44" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45">
-        <v>0.8</v>
-      </c>
-      <c r="D45" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="E45" s="1">
+        <v>71</v>
+      </c>
+      <c r="E45" s="1" t="str">
         <f>IF(COUNT(C45:D45)=2,D45*C45*IF(ISNUMBER(SEARCH("lcsc", F45)), U$2, 1),"")</f>
-        <v>0.4274400000000001</v>
-      </c>
-      <c r="F45" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>78</v>
+        <v/>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>73</v>
-      </c>
-      <c r="E46" s="1" t="str">
+        <v>21</v>
+      </c>
+      <c r="C46">
+        <v>1</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E46" s="1">
         <f>IF(COUNT(C46:D46)=2,D46*C46*IF(ISNUMBER(SEARCH("lcsc", F46)), U$2, 1),"")</f>
-        <v/>
+        <v>0.91790000000000016</v>
+      </c>
+      <c r="F46" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>21</v>
-      </c>
-      <c r="C47">
-        <v>1</v>
-      </c>
-      <c r="D47" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="E47" s="1">
-        <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
-        <v>0.91790000000000016</v>
-      </c>
-      <c r="F47" t="s">
-        <v>35</v>
+        <v>23</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>23</v>
+        <v>126</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
-      </c>
-      <c r="C48" t="s">
-        <v>29</v>
+        <v>127</v>
+      </c>
+      <c r="C48">
+        <v>0.02</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.26</v>
+      </c>
+      <c r="E48" s="1">
+        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
+        <v>7.124000000000001E-3</v>
+      </c>
+      <c r="F48" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
@@ -1713,7 +1748,7 @@
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B50" t="str">
         <f>TEXT("10", "#")</f>
@@ -1730,15 +1765,15 @@
         <v>0.51512000000000002</v>
       </c>
       <c r="F50" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="Q50" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -1753,100 +1788,203 @@
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>74</v>
+        <v>129</v>
+      </c>
+      <c r="E52" s="1" t="str">
+        <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D53" s="1">
-        <v>0.57999999999999996</v>
+        <v>9.81</v>
       </c>
       <c r="E53" s="1">
         <f>IF(COUNT(C53:D53)=2,D53*C53*IF(ISNUMBER(SEARCH("lcsc", F53)), U$2, 1),"")</f>
-        <v>1.1599999999999999</v>
+        <v>9.81</v>
       </c>
       <c r="F53" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>30</v>
-      </c>
-      <c r="E54" s="1" t="str">
+        <v>132</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2.39</v>
+      </c>
+      <c r="E54" s="1">
         <f>IF(COUNT(C54:D54)=2,D54*C54*IF(ISNUMBER(SEARCH("lcsc", F54)), U$2, 1),"")</f>
-        <v/>
+        <v>2.39</v>
+      </c>
+      <c r="F54" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" s="1">
-        <v>0.47</v>
+        <v>0.15</v>
       </c>
       <c r="E55" s="1">
         <f>IF(COUNT(C55:D55)=2,D55*C55*IF(ISNUMBER(SEARCH("lcsc", F55)), U$2, 1),"")</f>
-        <v>0.64390000000000003</v>
+        <v>0.15</v>
       </c>
       <c r="F55" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c r="C56">
         <v>1</v>
       </c>
       <c r="D56" s="1">
-        <v>0.5</v>
+        <v>0.15</v>
       </c>
       <c r="E56" s="1">
         <f>IF(COUNT(C56:D56)=2,D56*C56*IF(ISNUMBER(SEARCH("lcsc", F56)), U$2, 1),"")</f>
-        <v>0.68500000000000005</v>
+        <v>0.15</v>
       </c>
       <c r="F56" t="s">
-        <v>33</v>
+        <v>137</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>72</v>
+      </c>
+      <c r="E57" s="1" t="str">
+        <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="D58" s="1">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="E58" s="1">
+        <f>IF(COUNT(C58:D58)=2,D58*C58*IF(ISNUMBER(SEARCH("lcsc", F58)), U$2, 1),"")</f>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F58" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="E59" s="1">
+        <f>IF(COUNT(C59:D59)=2,D59*C59*IF(ISNUMBER(SEARCH("lcsc", F59)), U$2, 1),"")</f>
+        <v>3.48</v>
+      </c>
+      <c r="F59" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>30</v>
+      </c>
+      <c r="E60" s="1" t="str">
+        <f>IF(COUNT(C60:D60)=2,D60*C60*IF(ISNUMBER(SEARCH("lcsc", F60)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>73</v>
+      </c>
+      <c r="C61">
+        <v>1</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="E61" s="1">
+        <f>IF(COUNT(C61:D61)=2,D61*C61*IF(ISNUMBER(SEARCH("lcsc", F61)), U$2, 1),"")</f>
+        <v>0.64390000000000003</v>
+      </c>
+      <c r="F61" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>32</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="E62" s="1">
+        <f>IF(COUNT(C62:D62)=2,D62*C62*IF(ISNUMBER(SEARCH("lcsc", F62)), U$2, 1),"")</f>
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="F62" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
         <v>31</v>
       </c>
-      <c r="C57">
+      <c r="C63">
         <v>0.4</v>
       </c>
-      <c r="D57" s="1">
+      <c r="D63" s="1">
         <v>1.27</v>
       </c>
-      <c r="E57" s="1">
-        <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
+      <c r="E63" s="1">
+        <f>IF(COUNT(C63:D63)=2,D63*C63*IF(ISNUMBER(SEARCH("lcsc", F63)), U$2, 1),"")</f>
         <v>0.69596000000000002</v>
       </c>
-      <c r="F57" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="D58" s="1" t="s">
+      <c r="F63" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="D64" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E58" s="1">
-        <f>SUM(E2:E57)</f>
-        <v>92.664648000000014</v>
+      <c r="E64" s="1">
+        <f>SUM(E2:E63)</f>
+        <v>108.22433200000003</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LTC7890_Buck/LTC7890_BOM.xlsx
+++ b/projects/LTC7890_Buck/LTC7890_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LTC7890_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{243B72D3-0EB2-4F45-B68D-1E7300B3C5ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CE3451-132C-464E-88EF-46765E5E53D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="140">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -275,9 +275,6 @@
     <t xml:space="preserve">LTC7890RUJM#PBF </t>
   </si>
   <si>
-    <t>https://www.mouser.ca/ProductDetail/Analog-Devices/LTC7890RUJMPBF</t>
-  </si>
-  <si>
     <t>GanFET</t>
   </si>
   <si>
@@ -299,15 +296,6 @@
     <t>LDO</t>
   </si>
   <si>
-    <t>https://www.mouser.ca/ProductDetail/Infineon-Technologies/IGC025S08S1XTMA1</t>
-  </si>
-  <si>
-    <t>https://www.mouser.ca/ProductDetail/Same-Sky/HSB35-272725</t>
-  </si>
-  <si>
-    <t>https://www.mouser.ca/ProductDetail/Same-Sky/SLW-1478144-5A-S-D</t>
-  </si>
-  <si>
     <t>RT0603FRE07220KL</t>
   </si>
   <si>
@@ -386,9 +374,6 @@
     <t>https://www.lcsc.com/product-detail/C112305.html</t>
   </si>
   <si>
-    <t>https://www.mouser.ca/ProductDetail/MG-Chemicals/8329TCS-6ML</t>
-  </si>
-  <si>
     <t>8329TCS-6ML</t>
   </si>
   <si>
@@ -401,15 +386,9 @@
     <t>*18 out of 50</t>
   </si>
   <si>
-    <t>https://www.mouser.ca/ProductDetail/Samsung-Electro-Mechanics/CL32B475KCJZ4NE</t>
-  </si>
-  <si>
     <t>V3PM10-M3/H</t>
   </si>
   <si>
-    <t>https://www.mouser.ca/ProductDetail/Vishay-Semiconductors/V3PM10-M3-H</t>
-  </si>
-  <si>
     <t>RC0603FR-072R2L</t>
   </si>
   <si>
@@ -431,31 +410,52 @@
     <t>AUB0524VHD</t>
   </si>
   <si>
-    <t>https://www.mouser.ca/ProductDetail/Delta-Electronics/AUB0524VHD</t>
-  </si>
-  <si>
     <t>ADC101C021CIMM/NOPB</t>
   </si>
   <si>
-    <t>https://www.mouser.ca/ProductDetail/Texas-Instruments/ADC101C021CIMM-NOPB</t>
-  </si>
-  <si>
     <t>JSNB103F344FBEWH</t>
   </si>
   <si>
     <t>https://www.digikey.ca/en/products/detail/kamaya-inc/JSNB103F344FBEWH/25863556</t>
   </si>
   <si>
-    <t>GSF3400</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/good-ark-semiconductor/GSF3400/18648343</t>
-  </si>
-  <si>
     <t>CL-SB-13A-01T</t>
   </si>
   <si>
-    <t>https://www.mouser.ca/ProductDetail/Nidec-Components/CL-SB-13A-01T</t>
+    <t>PJA3438_R1_00001</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Same-Sky/SLW-1478144-5A-S-D?qs=IKkN%2F947nfC2U3%252B5gIoxgw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Analog-Devices-Inc/LTC7890RUJMPBF?qs=rQFj71Wb1eUkY2wEMbg5Ww%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Samsung-Electro-Mechanics/CL32B475KCJZ4NE?qs=CoAU%2FpHVZXyQaZt7yTSRCQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Infineon/IGC025S08S1XTMA1?qs=7%2F6SraaimPSYT343zJt1Kg%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Same-Sky/HSB35-272725?qs=ZcfC38r4PosSkJLoCalnmw%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/MG-Chemicals/8329TCS-6ML?qs=tfZGHB2PWd2lBHI%252BLjvf4Q%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Vishay/V3PM10-M3-H?qs=BJlw7L4Cy78AoJHh3Mh%2FVQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Delta-Electronics/AUB0524VHD?qs=%2FW4LtXOBxKvX%252B0X6HlUAuA%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Texas-Instruments/ADC101C021CIMM-NOPB?qs=7X5t%252BdzoRHBxGUwU7XIuhQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Panjit/PJA3438_R1_00001?qs=sPbYRqrBIVkvI0xzXAljBQ%3D%3D</t>
+  </si>
+  <si>
+    <t>https://www.mouser.ca/ProductDetail/Nidec/CL-SB-13A-01T?qs=XeJtXLiO41Sal7EI9lmQhg%3D%3D</t>
   </si>
 </sst>
 </file>
@@ -491,10 +491,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -829,12 +830,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E459BF-586A-4F4B-931A-B6F36BAD946F}">
-  <dimension ref="A1:U64"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="21.6328125" customWidth="1"/>
     <col min="4" max="4" width="9.08984375" style="1" customWidth="1"/>
     <col min="5" max="5" width="8.7265625" style="1"/>
+    <col min="20" max="20" width="9.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.35">
@@ -865,7 +867,7 @@
         <f t="shared" ref="E2" si="0">IF(COUNT(C2:D2)=2,D2*C2,"")</f>
         <v/>
       </c>
-      <c r="R2" t="s">
+      <c r="T2" t="s">
         <v>59</v>
       </c>
       <c r="U2">
@@ -887,7 +889,7 @@
         <v>12.82</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
@@ -938,7 +940,7 @@
         <v>5.52</v>
       </c>
       <c r="F6" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
@@ -961,8 +963,8 @@
       <c r="F7" t="s">
         <v>65</v>
       </c>
-      <c r="Q7" t="s">
-        <v>120</v>
+      <c r="S7" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
@@ -976,10 +978,10 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B9" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -992,7 +994,7 @@
         <v>4.6399999999999997</v>
       </c>
       <c r="F9" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
@@ -1018,7 +1020,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1" t="str">
         <f>IF(COUNT(C11:D11)=2,D11*C11*IF(ISNUMBER(SEARCH("lcsc", F11)), U$2, 1),"")</f>
@@ -1040,12 +1042,12 @@
         <v>25.24</v>
       </c>
       <c r="F12" t="s">
-        <v>87</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
@@ -1068,8 +1070,8 @@
       <c r="F14" t="s">
         <v>39</v>
       </c>
-      <c r="Q14" t="s">
-        <v>85</v>
+      <c r="S14" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
@@ -1089,7 +1091,7 @@
       <c r="F15" t="s">
         <v>37</v>
       </c>
-      <c r="Q15" t="s">
+      <c r="S15" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1113,11 +1115,11 @@
       <c r="F16" t="s">
         <v>46</v>
       </c>
-      <c r="Q16" t="s">
+      <c r="S16" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>7</v>
       </c>
@@ -1126,7 +1128,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -1147,7 +1149,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1156,7 +1158,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>55</v>
       </c>
@@ -1176,11 +1178,11 @@
       <c r="F20" t="s">
         <v>57</v>
       </c>
-      <c r="Q20" t="s">
+      <c r="S20" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1201,7 +1203,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -1221,13 +1223,13 @@
       <c r="F22" t="s">
         <v>67</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="S22" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="B23" t="str">
         <f>TEXT("100", "#")</f>
@@ -1244,13 +1246,13 @@
         <v>3.8360000000000009E-3</v>
       </c>
       <c r="F23" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q23" t="s">
+        <v>114</v>
+      </c>
+      <c r="S23" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -1259,7 +1261,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1274,12 +1276,12 @@
         <v>2.76</v>
       </c>
       <c r="F25" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C26">
         <v>1E-3</v>
@@ -1292,10 +1294,10 @@
         <v>4.1360000000000001E-2</v>
       </c>
       <c r="F26" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -1304,12 +1306,12 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="C28">
         <v>0.02</v>
@@ -1322,18 +1324,18 @@
         <v>1.3974000000000002E-2</v>
       </c>
       <c r="F28" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q28" t="s">
+        <v>103</v>
+      </c>
+      <c r="S28" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C29">
         <v>0.02</v>
@@ -1346,18 +1348,18 @@
         <v>2.2467999999999998E-2</v>
       </c>
       <c r="F29" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q29" t="s">
+        <v>95</v>
+      </c>
+      <c r="S29" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C30">
         <v>0.02</v>
@@ -1370,13 +1372,13 @@
         <v>1.6988E-2</v>
       </c>
       <c r="F30" t="s">
-        <v>112</v>
-      </c>
-      <c r="Q30" t="s">
+        <v>108</v>
+      </c>
+      <c r="S30" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>16</v>
       </c>
@@ -1385,27 +1387,27 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="C32">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D32" s="1">
         <v>0.53</v>
       </c>
       <c r="E32" s="1">
         <f t="shared" si="2"/>
-        <v>1.06</v>
+        <v>1.59</v>
       </c>
       <c r="F32" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B33" t="s">
         <v>10</v>
@@ -1421,15 +1423,15 @@
         <v>9.7269999999999995E-2</v>
       </c>
       <c r="F33" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q33" t="s">
+        <v>96</v>
+      </c>
+      <c r="S33" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="B34" t="str">
         <f>TEXT("2.2", "#.#")</f>
@@ -1446,15 +1448,15 @@
         <v>2.4660000000000005E-2</v>
       </c>
       <c r="F34" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q34" t="s">
+        <v>118</v>
+      </c>
+      <c r="S34" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="B35" t="str">
         <f>TEXT("1", "#")</f>
@@ -1471,18 +1473,18 @@
         <v>1.8632000000000003E-2</v>
       </c>
       <c r="F35" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q35" t="s">
+        <v>111</v>
+      </c>
+      <c r="S35" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
+        <v>81</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="C36">
         <v>0.04</v>
@@ -1495,13 +1497,13 @@
         <v>6.5760000000000002E-3</v>
       </c>
       <c r="F36" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+        <v>83</v>
+      </c>
+      <c r="S36" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>64</v>
       </c>
@@ -1516,12 +1518,12 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C38">
         <v>0.04</v>
@@ -1534,13 +1536,13 @@
         <v>1.6440000000000003E-2</v>
       </c>
       <c r="F38" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q38" t="s">
+        <v>88</v>
+      </c>
+      <c r="S38" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -1555,7 +1557,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -1575,16 +1577,16 @@
       <c r="F40" t="s">
         <v>43</v>
       </c>
-      <c r="Q40" t="s">
+      <c r="S40" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B41" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C41">
         <v>0.02</v>
@@ -1597,18 +1599,18 @@
         <v>1.4248000000000002E-2</v>
       </c>
       <c r="F41" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q41" t="s">
+        <v>91</v>
+      </c>
+      <c r="S41" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="B42" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C42">
         <v>0.02</v>
@@ -1621,13 +1623,13 @@
         <v>1.3974000000000002E-2</v>
       </c>
       <c r="F42" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q42" t="s">
+        <v>94</v>
+      </c>
+      <c r="S42" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>49</v>
       </c>
@@ -1645,7 +1647,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>27</v>
       </c>
@@ -1665,11 +1667,11 @@
       <c r="F44" t="s">
         <v>40</v>
       </c>
-      <c r="Q44" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S44" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>71</v>
       </c>
@@ -1678,7 +1680,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>21</v>
       </c>
@@ -1696,7 +1698,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>23</v>
       </c>
@@ -1707,12 +1709,12 @@
         <v>29</v>
       </c>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="B48" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="C48">
         <v>0.02</v>
@@ -1721,17 +1723,17 @@
         <v>0.26</v>
       </c>
       <c r="E48" s="1">
-        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
+        <f t="shared" ref="E48:E63" si="5">IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
         <v>7.124000000000001E-3</v>
       </c>
       <c r="F48" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q48" t="s">
+        <v>121</v>
+      </c>
+      <c r="S48" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>27</v>
       </c>
@@ -1742,13 +1744,13 @@
         <v>51</v>
       </c>
       <c r="E49" s="1" t="str">
-        <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B50" t="str">
         <f>TEXT("10", "#")</f>
@@ -1761,17 +1763,17 @@
         <v>0.94</v>
       </c>
       <c r="E50" s="1">
-        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
+        <f t="shared" si="5"/>
         <v>0.51512000000000002</v>
       </c>
       <c r="F50" t="s">
         <v>76</v>
       </c>
-      <c r="Q50" t="s">
+      <c r="S50" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>64</v>
       </c>
@@ -1782,76 +1784,66 @@
         <v>29</v>
       </c>
       <c r="E51" s="1" t="str">
-        <f>IF(COUNT(C51:D51)=2,D51*C51*IF(ISNUMBER(SEARCH("lcsc", F51)), U$2, 1),"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E52" s="1" t="str">
-        <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>130</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" s="1">
-        <v>9.81</v>
-      </c>
-      <c r="E53" s="1">
-        <f>IF(COUNT(C53:D53)=2,D53*C53*IF(ISNUMBER(SEARCH("lcsc", F53)), U$2, 1),"")</f>
-        <v>9.81</v>
-      </c>
-      <c r="F53" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+      <c r="C53" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>132</v>
+        <v>123</v>
       </c>
       <c r="C54">
         <v>1</v>
       </c>
       <c r="D54" s="1">
-        <v>2.39</v>
+        <v>9.81</v>
       </c>
       <c r="E54" s="1">
         <f>IF(COUNT(C54:D54)=2,D54*C54*IF(ISNUMBER(SEARCH("lcsc", F54)), U$2, 1),"")</f>
-        <v>2.39</v>
+        <v>9.81</v>
       </c>
       <c r="F54" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C55">
         <v>1</v>
       </c>
       <c r="D55" s="1">
-        <v>0.15</v>
+        <v>2.39</v>
       </c>
       <c r="E55" s="1">
         <f>IF(COUNT(C55:D55)=2,D55*C55*IF(ISNUMBER(SEARCH("lcsc", F55)), U$2, 1),"")</f>
-        <v>0.15</v>
+        <v>2.39</v>
       </c>
       <c r="F55" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -1864,127 +1856,145 @@
         <v>0.15</v>
       </c>
       <c r="F56" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0.32</v>
+      </c>
+      <c r="E57" s="1">
+        <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
+        <v>0.32</v>
+      </c>
+      <c r="F57" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
         <v>72</v>
       </c>
-      <c r="E57" s="1" t="str">
-        <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
+      <c r="E58" s="1" t="str">
+        <f>IF(COUNT(C58:D58)=2,D58*C58*IF(ISNUMBER(SEARCH("lcsc", F58)), U$2, 1),"")</f>
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
         <v>48</v>
-      </c>
-      <c r="C58">
-        <v>2</v>
-      </c>
-      <c r="D58" s="1">
-        <v>0.57999999999999996</v>
-      </c>
-      <c r="E58" s="1">
-        <f>IF(COUNT(C58:D58)=2,D58*C58*IF(ISNUMBER(SEARCH("lcsc", F58)), U$2, 1),"")</f>
-        <v>1.1599999999999999</v>
-      </c>
-      <c r="F58" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>138</v>
       </c>
       <c r="C59">
         <v>2</v>
       </c>
       <c r="D59" s="1">
-        <v>1.74</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="E59" s="1">
         <f>IF(COUNT(C59:D59)=2,D59*C59*IF(ISNUMBER(SEARCH("lcsc", F59)), U$2, 1),"")</f>
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>127</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60" s="1">
+        <v>1.74</v>
+      </c>
+      <c r="E60" s="1">
+        <f>IF(COUNT(C60:D60)=2,D60*C60*IF(ISNUMBER(SEARCH("lcsc", F60)), U$2, 1),"")</f>
         <v>3.48</v>
       </c>
-      <c r="F59" t="s">
+      <c r="F60" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
         <v>30</v>
       </c>
-      <c r="E60" s="1" t="str">
-        <f>IF(COUNT(C60:D60)=2,D60*C60*IF(ISNUMBER(SEARCH("lcsc", F60)), U$2, 1),"")</f>
+      <c r="E61" s="1" t="str">
+        <f>IF(COUNT(C61:D61)=2,D61*C61*IF(ISNUMBER(SEARCH("lcsc", F61)), U$2, 1),"")</f>
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
         <v>73</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61" s="1">
-        <v>0.47</v>
-      </c>
-      <c r="E61" s="1">
-        <f>IF(COUNT(C61:D61)=2,D61*C61*IF(ISNUMBER(SEARCH("lcsc", F61)), U$2, 1),"")</f>
-        <v>0.64390000000000003</v>
-      </c>
-      <c r="F61" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>32</v>
       </c>
       <c r="C62">
         <v>1</v>
       </c>
       <c r="D62" s="1">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="E62" s="1">
         <f>IF(COUNT(C62:D62)=2,D62*C62*IF(ISNUMBER(SEARCH("lcsc", F62)), U$2, 1),"")</f>
-        <v>0.68500000000000005</v>
+        <v>0.64390000000000003</v>
       </c>
       <c r="F62" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C63">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="D63" s="1">
-        <v>1.27</v>
+        <v>0.5</v>
       </c>
       <c r="E63" s="1">
         <f>IF(COUNT(C63:D63)=2,D63*C63*IF(ISNUMBER(SEARCH("lcsc", F63)), U$2, 1),"")</f>
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="F63" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>31</v>
+      </c>
+      <c r="C64">
+        <v>0.4</v>
+      </c>
+      <c r="D64" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="E64" s="1">
+        <f>IF(COUNT(C64:D64)=2,D64*C64*IF(ISNUMBER(SEARCH("lcsc", F64)), U$2, 1),"")</f>
         <v>0.69596000000000002</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F64" t="s">
         <v>75</v>
       </c>
-      <c r="Q63" t="s">
+      <c r="S64" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="D64" s="1" t="s">
+    <row r="65" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D65" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E64" s="1">
-        <f>SUM(E2:E63)</f>
-        <v>108.22433200000003</v>
+      <c r="E65" s="1">
+        <f>SUM(E2:E64)</f>
+        <v>108.92433200000002</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LTC7890_Buck/LTC7890_BOM.xlsx
+++ b/projects/LTC7890_Buck/LTC7890_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LTC7890_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CE3451-132C-464E-88EF-46765E5E53D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADDD79F-71CC-4645-960A-335645FC36F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="142">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -383,9 +383,6 @@
     <t>https://www.lcsc.com/product-detail/C105588.html</t>
   </si>
   <si>
-    <t>*18 out of 50</t>
-  </si>
-  <si>
     <t>V3PM10-M3/H</t>
   </si>
   <si>
@@ -456,6 +453,15 @@
   </si>
   <si>
     <t>https://www.mouser.ca/ProductDetail/Nidec/CL-SB-13A-01T?qs=XeJtXLiO41Sal7EI9lmQhg%3D%3D</t>
+  </si>
+  <si>
+    <t>Tallied Above (2x)</t>
+  </si>
+  <si>
+    <t>*20 out of 50</t>
+  </si>
+  <si>
+    <t>*4 out of 50</t>
   </si>
 </sst>
 </file>
@@ -491,11 +497,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -889,7 +894,7 @@
         <v>12.82</v>
       </c>
       <c r="F3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
@@ -940,7 +945,7 @@
         <v>5.52</v>
       </c>
       <c r="F6" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
@@ -951,20 +956,20 @@
         <v>13</v>
       </c>
       <c r="C7">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="D7" s="1">
         <v>0.33</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
-        <v>0.16275600000000001</v>
+        <v>0.18084000000000003</v>
       </c>
       <c r="F7" t="s">
         <v>65</v>
       </c>
       <c r="S7" t="s">
-        <v>115</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
@@ -1042,7 +1047,7 @@
         <v>25.24</v>
       </c>
       <c r="F12" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
@@ -1103,20 +1108,20 @@
         <v>45</v>
       </c>
       <c r="C16">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D16" s="1">
         <v>0.52</v>
       </c>
       <c r="E16" s="1">
         <f t="shared" si="2"/>
-        <v>2.8496000000000004E-2</v>
+        <v>5.6992000000000008E-2</v>
       </c>
       <c r="F16" t="s">
         <v>46</v>
       </c>
       <c r="S16" t="s">
-        <v>70</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
@@ -1276,7 +1281,7 @@
         <v>2.76</v>
       </c>
       <c r="F25" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
@@ -1294,7 +1299,7 @@
         <v>4.1360000000000001E-2</v>
       </c>
       <c r="F26" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
@@ -1389,7 +1394,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C32">
         <v>3</v>
@@ -1402,7 +1407,7 @@
         <v>1.59</v>
       </c>
       <c r="F32" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.35">
@@ -1431,7 +1436,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B34" t="str">
         <f>TEXT("2.2", "#.#")</f>
@@ -1448,7 +1453,7 @@
         <v>2.4660000000000005E-2</v>
       </c>
       <c r="F34" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="S34" t="s">
         <v>42</v>
@@ -1655,20 +1660,20 @@
         <v>28</v>
       </c>
       <c r="C44">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="D44" s="1">
         <v>0.52</v>
       </c>
       <c r="E44" s="1">
         <f t="shared" si="4"/>
-        <v>4.2744000000000004E-2</v>
+        <v>1.4248000000000002E-2</v>
       </c>
       <c r="F44" t="s">
         <v>40</v>
       </c>
       <c r="S44" t="s">
-        <v>84</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.35">
@@ -1711,10 +1716,10 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
+        <v>118</v>
+      </c>
+      <c r="B48" t="s">
         <v>119</v>
-      </c>
-      <c r="B48" t="s">
-        <v>120</v>
       </c>
       <c r="C48">
         <v>0.02</v>
@@ -1723,11 +1728,11 @@
         <v>0.26</v>
       </c>
       <c r="E48" s="1">
-        <f t="shared" ref="E48:E63" si="5">IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
+        <f t="shared" ref="E48:E52" si="5">IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
         <v>7.124000000000001E-3</v>
       </c>
       <c r="F48" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="S48" t="s">
         <v>36</v>
@@ -1735,71 +1740,67 @@
     </row>
     <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>27</v>
-      </c>
-      <c r="B49" t="s">
-        <v>28</v>
-      </c>
-      <c r="C49" t="s">
-        <v>51</v>
-      </c>
-      <c r="E49" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <v>80</v>
+      </c>
+      <c r="B49" t="str">
+        <f>TEXT("10", "#")</f>
+        <v>10</v>
+      </c>
+      <c r="C49">
+        <v>0.4</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="E49" s="1">
+        <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
+        <v>0.51512000000000002</v>
+      </c>
+      <c r="F49" t="s">
+        <v>76</v>
+      </c>
+      <c r="S49" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>80</v>
-      </c>
-      <c r="B50" t="str">
-        <f>TEXT("10", "#")</f>
-        <v>10</v>
-      </c>
-      <c r="C50">
-        <v>0.4</v>
-      </c>
-      <c r="D50" s="1">
-        <v>0.94</v>
-      </c>
-      <c r="E50" s="1">
-        <f t="shared" si="5"/>
-        <v>0.51512000000000002</v>
-      </c>
-      <c r="F50" t="s">
-        <v>76</v>
-      </c>
-      <c r="S50" t="s">
-        <v>77</v>
+        <v>64</v>
+      </c>
+      <c r="B50" t="s">
+        <v>13</v>
+      </c>
+      <c r="C50" t="s">
+        <v>139</v>
+      </c>
+      <c r="E50" s="1" t="str">
+        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="B51" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
-      </c>
-      <c r="E51" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <v>139</v>
       </c>
     </row>
     <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E52" s="1" t="str">
-        <f t="shared" si="5"/>
+        <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
         <v/>
       </c>
     </row>
     <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C53" t="s">
         <v>29</v>
@@ -1807,7 +1808,7 @@
     </row>
     <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C54">
         <v>1</v>
@@ -1820,12 +1821,12 @@
         <v>9.81</v>
       </c>
       <c r="F54" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C55">
         <v>1</v>
@@ -1838,12 +1839,12 @@
         <v>2.39</v>
       </c>
       <c r="F55" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C56">
         <v>1</v>
@@ -1856,12 +1857,12 @@
         <v>0.15</v>
       </c>
       <c r="F56" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C57">
         <v>1</v>
@@ -1874,7 +1875,7 @@
         <v>0.32</v>
       </c>
       <c r="F57" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="58" spans="1:19" x14ac:dyDescent="0.35">
@@ -1900,13 +1901,13 @@
         <f>IF(COUNT(C59:D59)=2,D59*C59*IF(ISNUMBER(SEARCH("lcsc", F59)), U$2, 1),"")</f>
         <v>1.1599999999999999</v>
       </c>
-      <c r="F59" s="3" t="s">
-        <v>129</v>
+      <c r="F59" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C60">
         <v>2</v>
@@ -1919,7 +1920,7 @@
         <v>3.48</v>
       </c>
       <c r="F60" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:19" x14ac:dyDescent="0.35">
@@ -1994,7 +1995,7 @@
       </c>
       <c r="E65" s="1">
         <f>SUM(E2:E64)</f>
-        <v>108.92433200000002</v>
+        <v>108.94241600000002</v>
       </c>
     </row>
   </sheetData>
